--- a/tools/MiniTemplate/Datas/__enums__.xlsx
+++ b/tools/MiniTemplate/Datas/__enums__.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\dd\ET\tools\MiniTemplate\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EF87CDB-8F88-4440-A8E3-3F6AEE68B24A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE047967-1EFE-4002-AA5E-D2B9EFB42C44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -205,12 +205,6 @@
     <t>Battle.HealType</t>
   </si>
   <si>
-    <t>Drop.Type</t>
-  </si>
-  <si>
-    <t>Drop.RewardType</t>
-  </si>
-  <si>
     <t>Event.Type</t>
   </si>
   <si>
@@ -1785,13 +1779,21 @@
   </si>
   <si>
     <t>Unit|Skill|Buff|Group</t>
+  </si>
+  <si>
+    <t>DropEnum.Type</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DropEnum.RewardType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1802,6 +1804,15 @@
     <font>
       <sz val="9"/>
       <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1861,15 +1872,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
@@ -1903,6 +1911,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2197,16 +2211,16 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
@@ -2215,31 +2229,31 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
+      <c r="I1" s="13"/>
+      <c r="J1" s="13"/>
+      <c r="K1" s="13"/>
+      <c r="L1" s="13"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
-      <c r="H2" s="3" t="s">
+      <c r="H2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="J2" s="2" t="s">
         <v>10</v>
       </c>
       <c r="K2" s="1" t="s">
@@ -2253,25 +2267,25 @@
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="3"/>
+      <c r="E3" s="2"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J3" s="2" t="s">
         <v>17</v>
       </c>
       <c r="K3" s="1" t="s">
@@ -2290,10 +2304,10 @@
         <v>1</v>
       </c>
       <c r="H4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="I4" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="J4">
         <v>1</v>
@@ -2301,10 +2315,10 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.4">
       <c r="H5" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="I5" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="J5">
         <v>2</v>
@@ -2312,10 +2326,10 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.4">
       <c r="H6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="I6" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="J6">
         <v>3</v>
@@ -2323,10 +2337,10 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.4">
       <c r="H7" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="I7" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="J7">
         <v>4</v>
@@ -2334,10 +2348,10 @@
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.4">
       <c r="H8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="I8" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="J8">
         <v>5</v>
@@ -2345,10 +2359,10 @@
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.4">
       <c r="H9" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="I9" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="J9">
         <v>6</v>
@@ -2365,10 +2379,10 @@
         <v>1</v>
       </c>
       <c r="H10" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I10" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -2376,10 +2390,10 @@
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.4">
       <c r="H11" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="I11" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="J11">
         <v>1</v>
@@ -2387,10 +2401,10 @@
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.4">
       <c r="H12" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="I12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J12">
         <v>2</v>
@@ -2398,10 +2412,10 @@
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.4">
       <c r="H13" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="I13" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="J13">
         <v>3</v>
@@ -2409,10 +2423,10 @@
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.4">
       <c r="H14" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="I14" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="J14">
         <v>4</v>
@@ -2420,10 +2434,10 @@
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.4">
       <c r="H15" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="I15" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="J15">
         <v>5</v>
@@ -2431,10 +2445,10 @@
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.4">
       <c r="H16" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="I16" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="J16">
         <v>6</v>
@@ -2442,429 +2456,429 @@
     </row>
     <row r="17" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H17" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I17" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="J17">
         <v>7</v>
       </c>
     </row>
     <row r="18" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C18" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="D18" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E18" s="4"/>
-      <c r="H18" s="4" t="s">
+      <c r="C18" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D18" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E18" s="3"/>
+      <c r="H18" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="J18" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="B19" s="3"/>
+      <c r="C19" s="3"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="H19" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="J19" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="B20" s="3"/>
+      <c r="C20" s="3"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="H20" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="I18" s="4" t="s">
+      <c r="I20" s="3" t="s">
         <v>330</v>
       </c>
-      <c r="J18" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B19" s="4"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
-      <c r="H19" s="4" t="s">
+      <c r="J20" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="B21" s="3"/>
+      <c r="C21" s="3"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+      <c r="H21" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="I19" s="4" t="s">
+      <c r="I21" s="3" t="s">
         <v>331</v>
       </c>
-      <c r="J19" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B20" s="4"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="4"/>
-      <c r="E20" s="4"/>
-      <c r="H20" s="4" t="s">
+      <c r="J21" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="B22" s="3"/>
+      <c r="C22" s="3"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
+      <c r="H22" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="I20" s="4" t="s">
+      <c r="I22" s="3" t="s">
         <v>332</v>
       </c>
-      <c r="J20" s="4">
+      <c r="J22" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="B23" s="3"/>
+      <c r="C23" s="3"/>
+      <c r="D23" s="3"/>
+      <c r="E23" s="3"/>
+      <c r="H23" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="J23" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="B24" s="3"/>
+      <c r="C24" s="3"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3"/>
+      <c r="H24" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="J24" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="B25" s="3"/>
+      <c r="C25" s="3"/>
+      <c r="D25" s="3"/>
+      <c r="E25" s="3"/>
+      <c r="H25" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="I25" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="J25" s="3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="B26" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C26" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D26" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E26" s="3"/>
+      <c r="H26" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="J26" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="B27" s="3"/>
+      <c r="C27" s="3"/>
+      <c r="D27" s="3"/>
+      <c r="E27" s="3"/>
+      <c r="H27" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="J27" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B21" s="4"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="4"/>
-      <c r="E21" s="4"/>
-      <c r="H21" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="I21" s="4" t="s">
-        <v>333</v>
-      </c>
-      <c r="J21" s="4">
+    <row r="28" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="B28" s="3"/>
+      <c r="C28" s="3"/>
+      <c r="D28" s="3"/>
+      <c r="E28" s="3"/>
+      <c r="H28" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="I28" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="J28" s="3">
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B22" s="4"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
-      <c r="H22" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="I22" s="4" t="s">
-        <v>334</v>
-      </c>
-      <c r="J22" s="4">
+    <row r="29" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="B29" s="3"/>
+      <c r="C29" s="3"/>
+      <c r="D29" s="3"/>
+      <c r="E29" s="3"/>
+      <c r="H29" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="J29" s="3">
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B23" s="4"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="4"/>
-      <c r="E23" s="4"/>
-      <c r="H23" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="I23" s="4" t="s">
-        <v>335</v>
-      </c>
-      <c r="J23" s="4">
+    <row r="30" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="B30" s="3"/>
+      <c r="C30" s="3"/>
+      <c r="D30" s="3"/>
+      <c r="E30" s="3"/>
+      <c r="H30" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="I30" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="J30" s="3">
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B24" s="4"/>
-      <c r="C24" s="4"/>
-      <c r="D24" s="4"/>
-      <c r="E24" s="4"/>
-      <c r="H24" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="I24" s="4" t="s">
-        <v>336</v>
-      </c>
-      <c r="J24" s="4">
+    <row r="31" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="B31" s="3"/>
+      <c r="C31" s="3"/>
+      <c r="D31" s="3"/>
+      <c r="E31" s="3"/>
+      <c r="H31" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="I31" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="J31" s="3">
         <v>6</v>
       </c>
     </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B25" s="4"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="4"/>
-      <c r="E25" s="4"/>
-      <c r="H25" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="I25" s="4" t="s">
-        <v>337</v>
-      </c>
-      <c r="J25" s="4">
+    <row r="32" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="B32" s="3"/>
+      <c r="C32" s="3"/>
+      <c r="D32" s="3"/>
+      <c r="E32" s="3"/>
+      <c r="H32" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="J32" s="3">
         <v>7</v>
       </c>
     </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B26" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C26" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="D26" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E26" s="4"/>
-      <c r="H26" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="I26" s="4" t="s">
-        <v>338</v>
-      </c>
-      <c r="J26" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B27" s="4"/>
-      <c r="C27" s="4"/>
-      <c r="D27" s="4"/>
-      <c r="E27" s="4"/>
-      <c r="H27" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="I27" s="4" t="s">
-        <v>339</v>
-      </c>
-      <c r="J27" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B28" s="4"/>
-      <c r="C28" s="4"/>
-      <c r="D28" s="4"/>
-      <c r="E28" s="4"/>
-      <c r="H28" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="I28" s="4" t="s">
-        <v>340</v>
-      </c>
-      <c r="J28" s="4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B29" s="4"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="4"/>
-      <c r="E29" s="4"/>
-      <c r="H29" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="I29" s="4" t="s">
-        <v>341</v>
-      </c>
-      <c r="J29" s="4">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B30" s="4"/>
-      <c r="C30" s="4"/>
-      <c r="D30" s="4"/>
-      <c r="E30" s="4"/>
-      <c r="H30" s="4" t="s">
+    <row r="33" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="B33" s="3"/>
+      <c r="C33" s="3"/>
+      <c r="D33" s="3"/>
+      <c r="E33" s="3"/>
+      <c r="H33" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="J33" s="3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="34" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="B34" s="3"/>
+      <c r="C34" s="3"/>
+      <c r="D34" s="3"/>
+      <c r="E34" s="3"/>
+      <c r="H34" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="I30" s="4" t="s">
-        <v>342</v>
-      </c>
-      <c r="J30" s="4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B31" s="4"/>
-      <c r="C31" s="4"/>
-      <c r="D31" s="4"/>
-      <c r="E31" s="4"/>
-      <c r="H31" s="4" t="s">
+      <c r="I34" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="J34" s="3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="35" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="B35" s="3"/>
+      <c r="C35" s="3"/>
+      <c r="D35" s="3"/>
+      <c r="E35" s="3"/>
+      <c r="H35" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="J35" s="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="36" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="B36" s="3"/>
+      <c r="C36" s="3"/>
+      <c r="D36" s="3"/>
+      <c r="E36" s="3"/>
+      <c r="H36" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="I31" s="4" t="s">
+      <c r="I36" s="3" t="s">
         <v>343</v>
       </c>
-      <c r="J31" s="4">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B32" s="4"/>
-      <c r="C32" s="4"/>
-      <c r="D32" s="4"/>
-      <c r="E32" s="4"/>
-      <c r="H32" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="I32" s="4" t="s">
+      <c r="J36" s="3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="37" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="B37" s="3"/>
+      <c r="C37" s="3"/>
+      <c r="D37" s="3"/>
+      <c r="E37" s="3"/>
+      <c r="H37" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I37" s="3" t="s">
         <v>344</v>
       </c>
-      <c r="J32" s="4">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="33" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B33" s="4"/>
-      <c r="C33" s="4"/>
-      <c r="D33" s="4"/>
-      <c r="E33" s="4"/>
-      <c r="H33" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="I33" s="4" t="s">
-        <v>317</v>
-      </c>
-      <c r="J33" s="4">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="34" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B34" s="4"/>
-      <c r="C34" s="4"/>
-      <c r="D34" s="4"/>
-      <c r="E34" s="4"/>
-      <c r="H34" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="I34" s="4" t="s">
+      <c r="J37" s="3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="38" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="B38" s="3"/>
+      <c r="C38" s="3"/>
+      <c r="D38" s="3"/>
+      <c r="E38" s="3"/>
+      <c r="H38" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="I38" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="J38" s="3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="39" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="B39" s="3"/>
+      <c r="C39" s="3"/>
+      <c r="D39" s="3"/>
+      <c r="E39" s="3"/>
+      <c r="H39" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="I39" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="J39" s="3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="40" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="B40" s="3"/>
+      <c r="C40" s="3"/>
+      <c r="D40" s="3"/>
+      <c r="E40" s="3"/>
+      <c r="H40" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="I40" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="J40" s="3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="41" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="B41" s="3"/>
+      <c r="C41" s="3"/>
+      <c r="D41" s="3"/>
+      <c r="E41" s="3"/>
+      <c r="H41" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="J41" s="3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="42" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="B42" s="3"/>
+      <c r="C42" s="3"/>
+      <c r="D42" s="3"/>
+      <c r="E42" s="3"/>
+      <c r="H42" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="I42" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="J34" s="4">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="35" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B35" s="4"/>
-      <c r="C35" s="4"/>
-      <c r="D35" s="4"/>
-      <c r="E35" s="4"/>
-      <c r="H35" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="I35" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="J35" s="4">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="36" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B36" s="4"/>
-      <c r="C36" s="4"/>
-      <c r="D36" s="4"/>
-      <c r="E36" s="4"/>
-      <c r="H36" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="I36" s="4" t="s">
-        <v>345</v>
-      </c>
-      <c r="J36" s="4">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="37" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B37" s="4"/>
-      <c r="C37" s="4"/>
-      <c r="D37" s="4"/>
-      <c r="E37" s="4"/>
-      <c r="H37" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="I37" s="4" t="s">
-        <v>346</v>
-      </c>
-      <c r="J37" s="4">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="38" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B38" s="4"/>
-      <c r="C38" s="4"/>
-      <c r="D38" s="4"/>
-      <c r="E38" s="4"/>
-      <c r="H38" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="I38" s="4" t="s">
-        <v>347</v>
-      </c>
-      <c r="J38" s="4">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="39" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B39" s="4"/>
-      <c r="C39" s="4"/>
-      <c r="D39" s="4"/>
-      <c r="E39" s="4"/>
-      <c r="H39" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="I39" s="4" t="s">
-        <v>348</v>
-      </c>
-      <c r="J39" s="4">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="40" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B40" s="4"/>
-      <c r="C40" s="4"/>
-      <c r="D40" s="4"/>
-      <c r="E40" s="4"/>
-      <c r="H40" s="4" t="s">
+      <c r="J42" s="3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="43" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="B43" s="3"/>
+      <c r="C43" s="3"/>
+      <c r="D43" s="3"/>
+      <c r="E43" s="3"/>
+      <c r="H43" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="I40" s="4" t="s">
+      <c r="I43" s="3" t="s">
         <v>349</v>
       </c>
-      <c r="J40" s="4">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="41" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B41" s="4"/>
-      <c r="C41" s="4"/>
-      <c r="D41" s="4"/>
-      <c r="E41" s="4"/>
-      <c r="H41" s="4" t="s">
+      <c r="J43" s="3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="44" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="B44" s="3"/>
+      <c r="C44" s="3"/>
+      <c r="D44" s="3"/>
+      <c r="E44" s="3"/>
+      <c r="H44" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="I41" s="4" t="s">
+      <c r="I44" s="3" t="s">
         <v>350</v>
       </c>
-      <c r="J41" s="4">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="42" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B42" s="4"/>
-      <c r="C42" s="4"/>
-      <c r="D42" s="4"/>
-      <c r="E42" s="4"/>
-      <c r="H42" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="I42" s="4" t="s">
-        <v>321</v>
-      </c>
-      <c r="J42" s="4">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="43" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B43" s="4"/>
-      <c r="C43" s="4"/>
-      <c r="D43" s="4"/>
-      <c r="E43" s="4"/>
-      <c r="H43" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="I43" s="4" t="s">
-        <v>351</v>
-      </c>
-      <c r="J43" s="4">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="44" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B44" s="4"/>
-      <c r="C44" s="4"/>
-      <c r="D44" s="4"/>
-      <c r="E44" s="4"/>
-      <c r="H44" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="I44" s="4" t="s">
-        <v>352</v>
-      </c>
-      <c r="J44" s="4">
+      <c r="J44" s="3">
         <v>19</v>
       </c>
     </row>
@@ -2879,10 +2893,10 @@
         <v>1</v>
       </c>
       <c r="H45" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="I45" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="J45">
         <v>1</v>
@@ -2890,10 +2904,10 @@
     </row>
     <row r="46" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H46" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="I46" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="J46">
         <v>2</v>
@@ -2901,10 +2915,10 @@
     </row>
     <row r="47" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H47" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="I47" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="J47">
         <v>3</v>
@@ -2912,10 +2926,10 @@
     </row>
     <row r="48" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H48" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="I48" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="J48">
         <v>4</v>
@@ -2923,10 +2937,10 @@
     </row>
     <row r="49" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H49" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="I49" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="J49">
         <v>5</v>
@@ -2943,7 +2957,7 @@
         <v>1</v>
       </c>
       <c r="H50" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="J50">
         <v>1</v>
@@ -2951,7 +2965,7 @@
     </row>
     <row r="51" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H51" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="J51">
         <v>2</v>
@@ -2959,7 +2973,7 @@
     </row>
     <row r="52" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H52" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="J52">
         <v>4</v>
@@ -2967,7 +2981,7 @@
     </row>
     <row r="53" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H53" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="J53">
         <v>8</v>
@@ -2975,39 +2989,39 @@
     </row>
     <row r="54" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H54" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="J54" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="55" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B55" s="4" t="s">
+      <c r="B55" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C55" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="D55" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E55" s="4"/>
-      <c r="H55" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="I55" s="4" t="s">
-        <v>357</v>
-      </c>
-      <c r="J55" s="4">
+      <c r="C55" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D55" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E55" s="3"/>
+      <c r="H55" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="I55" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="J55" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="56" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H56" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I56" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="J56">
         <v>2</v>
@@ -3015,10 +3029,10 @@
     </row>
     <row r="57" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H57" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="I57" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="J57">
         <v>3</v>
@@ -3026,42 +3040,42 @@
     </row>
     <row r="58" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H58" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="I58" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="J58">
         <v>4</v>
       </c>
     </row>
     <row r="59" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B59" s="4" t="s">
+      <c r="B59" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C59" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="D59" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E59" s="4"/>
-      <c r="H59" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="I59" s="4" t="s">
-        <v>361</v>
-      </c>
-      <c r="J59" s="4">
+      <c r="C59" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D59" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E59" s="3"/>
+      <c r="H59" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="J59" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="60" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H60" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I60" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="J60">
         <v>2</v>
@@ -3069,10 +3083,10 @@
     </row>
     <row r="61" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H61" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="I61" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="J61">
         <v>3</v>
@@ -3080,42 +3094,42 @@
     </row>
     <row r="62" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H62" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="I62" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="J62">
         <v>4</v>
       </c>
     </row>
     <row r="63" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B63" s="4" t="s">
+      <c r="B63" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C63" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="D63" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E63" s="4"/>
-      <c r="H63" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="I63" s="4" t="s">
-        <v>365</v>
-      </c>
-      <c r="J63" s="4">
+      <c r="C63" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D63" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E63" s="3"/>
+      <c r="H63" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="I63" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="J63" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="64" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H64" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="I64" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="J64">
         <v>2</v>
@@ -3123,10 +3137,10 @@
     </row>
     <row r="65" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H65" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="I65" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="J65">
         <v>3</v>
@@ -3134,53 +3148,53 @@
     </row>
     <row r="66" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H66" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="I66" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="J66">
         <v>4</v>
       </c>
     </row>
     <row r="67" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B67" s="4" t="s">
+      <c r="B67" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C67" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="D67" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E67" s="4"/>
-      <c r="H67" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="I67" s="4" t="s">
-        <v>365</v>
-      </c>
-      <c r="J67" s="4">
+      <c r="C67" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D67" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E67" s="3"/>
+      <c r="H67" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="I67" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="J67" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="68" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H68" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="I68" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="J68">
         <v>2</v>
       </c>
     </row>
     <row r="69" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="H69" s="6" t="s">
-        <v>129</v>
+      <c r="H69" s="5" t="s">
+        <v>127</v>
       </c>
       <c r="I69" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="J69">
         <v>3</v>
@@ -3188,42 +3202,42 @@
     </row>
     <row r="70" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H70" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="I70" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="J70">
         <v>4</v>
       </c>
     </row>
     <row r="71" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B71" s="4" t="s">
+      <c r="B71" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C71" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="D71" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E71" s="4"/>
-      <c r="H71" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="I71" s="4" t="s">
-        <v>372</v>
-      </c>
-      <c r="J71" s="4">
+      <c r="C71" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D71" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E71" s="3"/>
+      <c r="H71" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="I71" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="J71" s="3">
         <v>100</v>
       </c>
     </row>
     <row r="72" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="H72" s="6" t="s">
-        <v>131</v>
+      <c r="H72" s="5" t="s">
+        <v>129</v>
       </c>
       <c r="I72" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="J72">
         <v>1</v>
@@ -3231,10 +3245,10 @@
     </row>
     <row r="73" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H73" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="I73" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="J73">
         <v>2</v>
@@ -3242,10 +3256,10 @@
     </row>
     <row r="74" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H74" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="I74" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="J74">
         <v>3</v>
@@ -3253,10 +3267,10 @@
     </row>
     <row r="75" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H75" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="I75" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="J75">
         <v>4</v>
@@ -3264,74 +3278,74 @@
     </row>
     <row r="76" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H76" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="I76" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="J76" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
     </row>
     <row r="77" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B77" s="4" t="s">
+      <c r="B77" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C77" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="D77" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E77" s="4"/>
-      <c r="H77" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="I77" s="4" t="s">
-        <v>378</v>
-      </c>
-      <c r="J77" s="4">
+      <c r="C77" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D77" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E77" s="3"/>
+      <c r="H77" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="I77" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="J77" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="78" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H78" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I78" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="J78">
         <v>1</v>
       </c>
     </row>
     <row r="79" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B79" s="4" t="s">
+      <c r="B79" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C79" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="D79" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E79" s="4"/>
-      <c r="H79" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="I79" s="4" t="s">
-        <v>380</v>
-      </c>
-      <c r="J79" s="4">
+      <c r="C79" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D79" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E79" s="3"/>
+      <c r="H79" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="I79" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="J79" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="80" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H80" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="I80" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="J80">
         <v>1</v>
@@ -3339,10 +3353,10 @@
     </row>
     <row r="81" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H81" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="I81" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="J81">
         <v>2</v>
@@ -3350,42 +3364,42 @@
     </row>
     <row r="82" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H82" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="I82" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="J82">
         <v>3</v>
       </c>
     </row>
     <row r="83" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B83" s="4" t="s">
+      <c r="B83" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C83" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="D83" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E83" s="4"/>
-      <c r="H83" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="I83" s="4" t="s">
-        <v>383</v>
-      </c>
-      <c r="J83" s="4">
+      <c r="C83" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D83" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E83" s="3"/>
+      <c r="H83" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="J83" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="84" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H84" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="I84" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="J84">
         <v>2</v>
@@ -3393,21 +3407,21 @@
     </row>
     <row r="85" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H85" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="I85" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="J85">
         <v>3</v>
       </c>
     </row>
     <row r="86" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="H86" s="8" t="s">
-        <v>143</v>
+      <c r="H86" s="7" t="s">
+        <v>141</v>
       </c>
       <c r="I86" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="J86">
         <v>4</v>
@@ -3415,10 +3429,10 @@
     </row>
     <row r="87" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H87" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="I87" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="J87">
         <v>10</v>
@@ -3426,10 +3440,10 @@
     </row>
     <row r="88" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H88" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="I88" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="J88">
         <v>11</v>
@@ -3437,10 +3451,10 @@
     </row>
     <row r="89" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H89" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="I89" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="J89">
         <v>100</v>
@@ -3448,10 +3462,10 @@
     </row>
     <row r="90" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H90" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="I90" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="J90">
         <v>101</v>
@@ -3468,10 +3482,10 @@
         <v>1</v>
       </c>
       <c r="H91" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I91" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="J91">
         <v>0</v>
@@ -3479,10 +3493,10 @@
     </row>
     <row r="92" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H92" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="I92" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="J92">
         <v>1</v>
@@ -3490,10 +3504,10 @@
     </row>
     <row r="93" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H93" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="I93" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="J93">
         <v>2</v>
@@ -3501,10 +3515,10 @@
     </row>
     <row r="94" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H94" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="I94" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="J94">
         <v>3</v>
@@ -3512,10 +3526,10 @@
     </row>
     <row r="95" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H95" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="I95" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="J95">
         <v>4</v>
@@ -3523,10 +3537,10 @@
     </row>
     <row r="96" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H96" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="I96" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="J96">
         <v>5</v>
@@ -3534,10 +3548,10 @@
     </row>
     <row r="97" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H97" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I97" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="J97">
         <v>6</v>
@@ -3545,42 +3559,42 @@
     </row>
     <row r="98" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H98" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="I98" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="J98">
         <v>7</v>
       </c>
     </row>
     <row r="99" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B99" s="4" t="s">
+      <c r="B99" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C99" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="D99" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E99" s="4"/>
-      <c r="H99" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="I99" s="4" t="s">
-        <v>395</v>
-      </c>
-      <c r="J99" s="4">
+      <c r="C99" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D99" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E99" s="3"/>
+      <c r="H99" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="I99" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="J99" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="100" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H100" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="I100" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="J100">
         <v>1</v>
@@ -3597,10 +3611,10 @@
         <v>1</v>
       </c>
       <c r="H101" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="I101" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="J101">
         <v>100</v>
@@ -3608,10 +3622,10 @@
     </row>
     <row r="102" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H102" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="I102" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="J102">
         <v>1</v>
@@ -3619,10 +3633,10 @@
     </row>
     <row r="103" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H103" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="I103" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="J103">
         <v>2</v>
@@ -3630,10 +3644,10 @@
     </row>
     <row r="104" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H104" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="I104" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="J104">
         <v>3</v>
@@ -3641,10 +3655,10 @@
     </row>
     <row r="105" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H105" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="I105" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="J105">
         <v>4</v>
@@ -3652,10 +3666,10 @@
     </row>
     <row r="106" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H106" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="I106" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="J106">
         <v>5</v>
@@ -3663,10 +3677,10 @@
     </row>
     <row r="107" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H107" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="I107" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="J107">
         <v>6</v>
@@ -3674,10 +3688,10 @@
     </row>
     <row r="108" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H108" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="I108" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="J108">
         <v>7</v>
@@ -3685,10 +3699,10 @@
     </row>
     <row r="109" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H109" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="I109" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="J109">
         <v>8</v>
@@ -3696,10 +3710,10 @@
     </row>
     <row r="110" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H110" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="I110" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="J110">
         <v>9</v>
@@ -3707,10 +3721,10 @@
     </row>
     <row r="111" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H111" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="I111" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="J111">
         <v>10</v>
@@ -3718,10 +3732,10 @@
     </row>
     <row r="112" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H112" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="I112" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="J112">
         <v>11</v>
@@ -3729,13 +3743,13 @@
     </row>
     <row r="113" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H113" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="I113" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="J113" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="114" spans="2:10" x14ac:dyDescent="0.4">
@@ -3749,10 +3763,10 @@
         <v>1</v>
       </c>
       <c r="H114" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I114" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="J114">
         <v>0</v>
@@ -3760,10 +3774,10 @@
     </row>
     <row r="115" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H115" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="I115" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="J115">
         <v>1</v>
@@ -3771,10 +3785,10 @@
     </row>
     <row r="116" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H116" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="I116" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="J116">
         <v>2</v>
@@ -3782,10 +3796,10 @@
     </row>
     <row r="117" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H117" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="I117" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="J117">
         <v>3</v>
@@ -3793,10 +3807,10 @@
     </row>
     <row r="118" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H118" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="I118" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="J118">
         <v>4</v>
@@ -3804,10 +3818,10 @@
     </row>
     <row r="119" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H119" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="I119" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="J119">
         <v>5</v>
@@ -3815,10 +3829,10 @@
     </row>
     <row r="120" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H120" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="I120" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="J120">
         <v>6</v>
@@ -3826,10 +3840,10 @@
     </row>
     <row r="121" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H121" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="I121" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="J121">
         <v>7</v>
@@ -3837,10 +3851,10 @@
     </row>
     <row r="122" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H122" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I122" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="J122">
         <v>8</v>
@@ -3848,10 +3862,10 @@
     </row>
     <row r="123" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H123" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I123" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="J123">
         <v>9</v>
@@ -3859,10 +3873,10 @@
     </row>
     <row r="124" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H124" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="I124" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="J124">
         <v>10</v>
@@ -3870,10 +3884,10 @@
     </row>
     <row r="125" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H125" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="I125" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="J125">
         <v>11</v>
@@ -3881,10 +3895,10 @@
     </row>
     <row r="126" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H126" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I126" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="J126">
         <v>12</v>
@@ -3892,10 +3906,10 @@
     </row>
     <row r="127" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H127" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="I127" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="J127">
         <v>13</v>
@@ -3903,10 +3917,10 @@
     </row>
     <row r="128" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H128" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="I128" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="J128">
         <v>14</v>
@@ -3914,10 +3928,10 @@
     </row>
     <row r="129" spans="8:10" x14ac:dyDescent="0.4">
       <c r="H129" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="I129" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="J129">
         <v>15</v>
@@ -3925,10 +3939,10 @@
     </row>
     <row r="130" spans="8:10" x14ac:dyDescent="0.4">
       <c r="H130" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="I130" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="J130">
         <v>16</v>
@@ -3936,10 +3950,10 @@
     </row>
     <row r="131" spans="8:10" x14ac:dyDescent="0.4">
       <c r="H131" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="I131" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="J131">
         <v>17</v>
@@ -3947,10 +3961,10 @@
     </row>
     <row r="132" spans="8:10" x14ac:dyDescent="0.4">
       <c r="H132" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="I132" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="J132">
         <v>18</v>
@@ -3958,10 +3972,10 @@
     </row>
     <row r="133" spans="8:10" x14ac:dyDescent="0.4">
       <c r="H133" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="I133" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="J133">
         <v>19</v>
@@ -3969,10 +3983,10 @@
     </row>
     <row r="134" spans="8:10" x14ac:dyDescent="0.4">
       <c r="H134" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="I134" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="J134">
         <v>20</v>
@@ -3980,10 +3994,10 @@
     </row>
     <row r="135" spans="8:10" x14ac:dyDescent="0.4">
       <c r="H135" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="I135" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="J135">
         <v>21</v>
@@ -3991,10 +4005,10 @@
     </row>
     <row r="136" spans="8:10" x14ac:dyDescent="0.4">
       <c r="H136" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="I136" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="J136">
         <v>22</v>
@@ -4002,10 +4016,10 @@
     </row>
     <row r="137" spans="8:10" x14ac:dyDescent="0.4">
       <c r="H137" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="I137" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="J137">
         <v>23</v>
@@ -4013,10 +4027,10 @@
     </row>
     <row r="138" spans="8:10" x14ac:dyDescent="0.4">
       <c r="H138" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="I138" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="J138">
         <v>24</v>
@@ -4024,10 +4038,10 @@
     </row>
     <row r="139" spans="8:10" x14ac:dyDescent="0.4">
       <c r="H139" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="I139" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="J139">
         <v>25</v>
@@ -4035,10 +4049,10 @@
     </row>
     <row r="140" spans="8:10" x14ac:dyDescent="0.4">
       <c r="H140" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="I140" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="J140">
         <v>26</v>
@@ -4046,10 +4060,10 @@
     </row>
     <row r="141" spans="8:10" x14ac:dyDescent="0.4">
       <c r="H141" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="I141" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="J141">
         <v>27</v>
@@ -4057,10 +4071,10 @@
     </row>
     <row r="142" spans="8:10" x14ac:dyDescent="0.4">
       <c r="H142" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="I142" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="J142">
         <v>28</v>
@@ -4068,10 +4082,10 @@
     </row>
     <row r="143" spans="8:10" x14ac:dyDescent="0.4">
       <c r="H143" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="I143" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="J143">
         <v>29</v>
@@ -4079,10 +4093,10 @@
     </row>
     <row r="144" spans="8:10" x14ac:dyDescent="0.4">
       <c r="H144" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="I144" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="J144">
         <v>30</v>
@@ -4090,10 +4104,10 @@
     </row>
     <row r="145" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H145" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="I145" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="J145">
         <v>31</v>
@@ -4101,10 +4115,10 @@
     </row>
     <row r="146" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H146" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="I146" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="J146">
         <v>32</v>
@@ -4121,10 +4135,10 @@
         <v>1</v>
       </c>
       <c r="H147" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="I147" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="J147">
         <v>0</v>
@@ -4132,10 +4146,10 @@
     </row>
     <row r="148" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H148" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="I148" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="J148">
         <v>1</v>
@@ -4143,10 +4157,10 @@
     </row>
     <row r="149" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H149" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="I149" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="J149">
         <v>2</v>
@@ -4163,10 +4177,10 @@
         <v>1</v>
       </c>
       <c r="H150" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="I150" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="J150">
         <v>0</v>
@@ -4174,10 +4188,10 @@
     </row>
     <row r="151" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H151" t="s">
-        <v>201</v>
-      </c>
-      <c r="I151" s="6" t="s">
-        <v>445</v>
+        <v>199</v>
+      </c>
+      <c r="I151" s="5" t="s">
+        <v>443</v>
       </c>
       <c r="J151">
         <v>1</v>
@@ -4185,54 +4199,54 @@
     </row>
     <row r="152" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H152" t="s">
-        <v>202</v>
-      </c>
-      <c r="I152" s="6" t="s">
-        <v>446</v>
+        <v>200</v>
+      </c>
+      <c r="I152" s="5" t="s">
+        <v>444</v>
       </c>
       <c r="J152">
         <v>2</v>
       </c>
     </row>
     <row r="153" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="H153" s="8" t="s">
-        <v>203</v>
-      </c>
-      <c r="I153" s="6" t="s">
-        <v>447</v>
+      <c r="H153" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="I153" s="5" t="s">
+        <v>445</v>
       </c>
       <c r="J153">
         <v>3</v>
       </c>
     </row>
     <row r="154" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="H154" s="8" t="s">
-        <v>143</v>
+      <c r="H154" s="7" t="s">
+        <v>141</v>
       </c>
       <c r="I154" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="J154">
         <v>4</v>
       </c>
     </row>
     <row r="155" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="H155" s="8" t="s">
-        <v>204</v>
+      <c r="H155" s="7" t="s">
+        <v>202</v>
       </c>
       <c r="I155" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="J155">
         <v>5</v>
       </c>
     </row>
     <row r="156" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="H156" s="8" t="s">
-        <v>205</v>
+      <c r="H156" s="7" t="s">
+        <v>203</v>
       </c>
       <c r="I156" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="J156">
         <v>6</v>
@@ -4249,10 +4263,10 @@
         <v>1</v>
       </c>
       <c r="H157" t="s">
-        <v>206</v>
-      </c>
-      <c r="I157" s="6" t="s">
-        <v>450</v>
+        <v>204</v>
+      </c>
+      <c r="I157" s="5" t="s">
+        <v>448</v>
       </c>
       <c r="J157">
         <v>0</v>
@@ -4260,10 +4274,10 @@
     </row>
     <row r="158" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H158" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="I158" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="J158">
         <v>1</v>
@@ -4271,10 +4285,10 @@
     </row>
     <row r="159" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H159" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="I159" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="J159">
         <v>2</v>
@@ -4291,10 +4305,10 @@
         <v>1</v>
       </c>
       <c r="H160" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="I160" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="J160">
         <v>1</v>
@@ -4302,10 +4316,10 @@
     </row>
     <row r="161" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H161" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I161" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="J161">
         <v>2</v>
@@ -4313,10 +4327,10 @@
     </row>
     <row r="162" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H162" t="s">
-        <v>95</v>
-      </c>
-      <c r="I162" s="11" t="s">
-        <v>455</v>
+        <v>93</v>
+      </c>
+      <c r="I162" s="10" t="s">
+        <v>453</v>
       </c>
       <c r="J162">
         <v>3</v>
@@ -4333,10 +4347,10 @@
         <v>1</v>
       </c>
       <c r="H163" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="I163" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="J163">
         <v>1</v>
@@ -4344,10 +4358,10 @@
     </row>
     <row r="164" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H164" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="I164" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="J164">
         <v>2</v>
@@ -4355,10 +4369,10 @@
     </row>
     <row r="165" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H165" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="I165" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="J165">
         <v>3</v>
@@ -4366,10 +4380,10 @@
     </row>
     <row r="166" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H166" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="I166" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="J166">
         <v>4</v>
@@ -4386,10 +4400,10 @@
         <v>1</v>
       </c>
       <c r="H167" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="I167" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="J167">
         <v>0</v>
@@ -4397,10 +4411,10 @@
     </row>
     <row r="168" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H168" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="I168" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="J168">
         <v>1</v>
@@ -4417,10 +4431,10 @@
         <v>1</v>
       </c>
       <c r="H169" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="I169" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="J169">
         <v>0</v>
@@ -4428,10 +4442,10 @@
     </row>
     <row r="170" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H170" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="I170" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="J170">
         <v>1</v>
@@ -4439,10 +4453,10 @@
     </row>
     <row r="171" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H171" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="I171" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="J171">
         <v>2</v>
@@ -4459,10 +4473,10 @@
         <v>1</v>
       </c>
       <c r="H172" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="I172" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="J172">
         <v>0</v>
@@ -4470,10 +4484,10 @@
     </row>
     <row r="173" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H173" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="I173" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="J173">
         <v>1</v>
@@ -4490,10 +4504,10 @@
         <v>1</v>
       </c>
       <c r="H174" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I174" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="J174">
         <v>0</v>
@@ -4501,10 +4515,10 @@
     </row>
     <row r="175" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H175" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="I175" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="J175">
         <v>1</v>
@@ -4512,10 +4526,10 @@
     </row>
     <row r="176" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H176" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="I176" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="J176">
         <v>2</v>
@@ -4523,10 +4537,10 @@
     </row>
     <row r="177" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H177" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="I177" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="J177">
         <v>3</v>
@@ -4543,10 +4557,10 @@
         <v>1</v>
       </c>
       <c r="H178" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I178" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="J178">
         <v>0</v>
@@ -4554,10 +4568,10 @@
     </row>
     <row r="179" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H179" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="I179" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="J179">
         <v>1</v>
@@ -4565,10 +4579,10 @@
     </row>
     <row r="180" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H180" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="I180" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="J180">
         <v>2</v>
@@ -4585,10 +4599,10 @@
         <v>1</v>
       </c>
       <c r="H181" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="I181" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="J181">
         <v>0</v>
@@ -4596,10 +4610,10 @@
     </row>
     <row r="182" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H182" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="I182" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="J182">
         <v>1</v>
@@ -4607,10 +4621,10 @@
     </row>
     <row r="183" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H183" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="I183" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="J183">
         <v>2</v>
@@ -4618,10 +4632,10 @@
     </row>
     <row r="184" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H184" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="I184" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="J184">
         <v>3</v>
@@ -4629,10 +4643,10 @@
     </row>
     <row r="185" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H185" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="I185" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="J185">
         <v>4</v>
@@ -4640,10 +4654,10 @@
     </row>
     <row r="186" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H186" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="I186" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="J186">
         <v>5</v>
@@ -4660,10 +4674,10 @@
         <v>1</v>
       </c>
       <c r="H187" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="I187" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="J187">
         <v>0</v>
@@ -4671,10 +4685,10 @@
     </row>
     <row r="188" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H188" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="I188" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="J188">
         <v>1</v>
@@ -4682,10 +4696,10 @@
     </row>
     <row r="189" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H189" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="I189" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J189">
         <v>3</v>
@@ -4693,10 +4707,10 @@
     </row>
     <row r="190" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H190" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="I190" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="J190">
         <v>4</v>
@@ -4713,10 +4727,10 @@
         <v>1</v>
       </c>
       <c r="H191" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I191" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="J191">
         <v>0</v>
@@ -4724,10 +4738,10 @@
     </row>
     <row r="192" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H192" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="I192" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="J192">
         <v>1</v>
@@ -4735,10 +4749,10 @@
     </row>
     <row r="193" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H193" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="I193" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="J193">
         <v>2</v>
@@ -4755,10 +4769,10 @@
         <v>1</v>
       </c>
       <c r="H194" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="I194" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="J194">
         <v>0</v>
@@ -4766,10 +4780,10 @@
     </row>
     <row r="195" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H195" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="I195" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="J195">
         <v>1</v>
@@ -4777,10 +4791,10 @@
     </row>
     <row r="196" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H196" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="I196" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="J196">
         <v>2</v>
@@ -4788,10 +4802,10 @@
     </row>
     <row r="197" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H197" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="I197" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="J197">
         <v>3</v>
@@ -4799,10 +4813,10 @@
     </row>
     <row r="198" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H198" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="I198" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="J198">
         <v>4</v>
@@ -4810,10 +4824,10 @@
     </row>
     <row r="199" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H199" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="I199" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="J199">
         <v>5</v>
@@ -4830,10 +4844,10 @@
         <v>1</v>
       </c>
       <c r="H200" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="I200" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="J200">
         <v>0</v>
@@ -4841,10 +4855,10 @@
     </row>
     <row r="201" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H201" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="I201" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="J201">
         <v>1</v>
@@ -4852,10 +4866,10 @@
     </row>
     <row r="202" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H202" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="I202" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="J202">
         <v>2</v>
@@ -4863,10 +4877,10 @@
     </row>
     <row r="203" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H203" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="I203" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="J203">
         <v>3</v>
@@ -4874,10 +4888,10 @@
     </row>
     <row r="204" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H204" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="I204" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="J204">
         <v>4</v>
@@ -4885,10 +4899,10 @@
     </row>
     <row r="205" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H205" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="I205" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="J205">
         <v>5</v>
@@ -4896,10 +4910,10 @@
     </row>
     <row r="206" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H206" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="I206" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="J206">
         <v>20</v>
@@ -4907,10 +4921,10 @@
     </row>
     <row r="207" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H207" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="I207" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="J207">
         <v>21</v>
@@ -4918,10 +4932,10 @@
     </row>
     <row r="208" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H208" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="I208" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="J208">
         <v>22</v>
@@ -4929,10 +4943,10 @@
     </row>
     <row r="209" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H209" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="I209" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="J209">
         <v>23</v>
@@ -4940,10 +4954,10 @@
     </row>
     <row r="210" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H210" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="I210" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="J210">
         <v>24</v>
@@ -4951,10 +4965,10 @@
     </row>
     <row r="211" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H211" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="I211" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="J211">
         <v>25</v>
@@ -4962,10 +4976,10 @@
     </row>
     <row r="212" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H212" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="I212" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="J212">
         <v>26</v>
@@ -4973,10 +4987,10 @@
     </row>
     <row r="213" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H213" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="I213" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="J213">
         <v>27</v>
@@ -4993,10 +5007,10 @@
         <v>1</v>
       </c>
       <c r="H214" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="I214" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="J214">
         <v>0</v>
@@ -5004,10 +5018,10 @@
     </row>
     <row r="215" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H215" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="I215" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="J215">
         <v>1</v>
@@ -5015,10 +5029,10 @@
     </row>
     <row r="216" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H216" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="I216" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="J216">
         <v>2</v>
@@ -5035,10 +5049,10 @@
         <v>1</v>
       </c>
       <c r="H217" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I217" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="J217">
         <v>0</v>
@@ -5046,10 +5060,10 @@
     </row>
     <row r="218" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H218" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="I218" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="J218">
         <v>1</v>
@@ -5057,10 +5071,10 @@
     </row>
     <row r="219" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H219" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="I219" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="J219">
         <v>2</v>
@@ -5068,10 +5082,10 @@
     </row>
     <row r="220" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H220" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="I220" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="J220">
         <v>3</v>
@@ -5079,10 +5093,10 @@
     </row>
     <row r="221" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H221" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="I221" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="J221">
         <v>4</v>
@@ -5090,10 +5104,10 @@
     </row>
     <row r="222" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H222" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="I222" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="J222">
         <v>6</v>
@@ -5101,10 +5115,10 @@
     </row>
     <row r="223" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H223" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="I223" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="J223">
         <v>7</v>
@@ -5121,10 +5135,10 @@
         <v>1</v>
       </c>
       <c r="H224" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="I224" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="J224">
         <v>0</v>
@@ -5132,10 +5146,10 @@
     </row>
     <row r="225" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H225" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="I225" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="J225">
         <v>1</v>
@@ -5143,10 +5157,10 @@
     </row>
     <row r="226" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H226" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="I226" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="J226">
         <v>2</v>
@@ -5154,10 +5168,10 @@
     </row>
     <row r="227" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H227" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="I227" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="J227">
         <v>3</v>
@@ -5165,10 +5179,10 @@
     </row>
     <row r="228" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H228" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="I228" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="J228">
         <v>4</v>
@@ -5185,57 +5199,57 @@
         <v>1</v>
       </c>
       <c r="H229" t="s">
+        <v>255</v>
+      </c>
+      <c r="I229" t="s">
+        <v>509</v>
+      </c>
+      <c r="J229">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="230" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="H230" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="I230" s="8" t="s">
+        <v>510</v>
+      </c>
+      <c r="J230" s="11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="231" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="H231" s="8" t="s">
+        <v>256</v>
+      </c>
+      <c r="I231" s="8" t="s">
+        <v>511</v>
+      </c>
+      <c r="J231" s="11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="232" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="H232" s="8" t="s">
         <v>257</v>
       </c>
-      <c r="I229" t="s">
-        <v>511</v>
-      </c>
-      <c r="J229">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="230" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="H230" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="I230" s="9" t="s">
+      <c r="I232" s="8" t="s">
         <v>512</v>
       </c>
-      <c r="J230" s="12">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="231" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="H231" s="9" t="s">
-        <v>258</v>
-      </c>
-      <c r="I231" s="9" t="s">
-        <v>513</v>
-      </c>
-      <c r="J231" s="12">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="232" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="H232" s="9" t="s">
-        <v>259</v>
-      </c>
-      <c r="I232" s="9" t="s">
-        <v>514</v>
-      </c>
-      <c r="J232" s="12">
+      <c r="J232" s="11">
         <v>4</v>
       </c>
     </row>
     <row r="233" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="H233" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="I233" s="9" t="s">
-        <v>408</v>
-      </c>
-      <c r="J233" s="12" t="s">
-        <v>587</v>
+      <c r="H233" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="I233" s="8" t="s">
+        <v>406</v>
+      </c>
+      <c r="J233" s="11" t="s">
+        <v>585</v>
       </c>
     </row>
     <row r="234" spans="2:10" x14ac:dyDescent="0.4">
@@ -5248,398 +5262,398 @@
       <c r="D234" t="b">
         <v>1</v>
       </c>
-      <c r="H234" s="9" t="s">
+      <c r="H234" s="8" t="s">
+        <v>258</v>
+      </c>
+      <c r="I234" s="8" t="s">
+        <v>513</v>
+      </c>
+      <c r="J234" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="235" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="H235" s="8" t="s">
+        <v>259</v>
+      </c>
+      <c r="I235" s="8" t="s">
+        <v>514</v>
+      </c>
+      <c r="J235" s="11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="236" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="H236" s="8" t="s">
         <v>260</v>
       </c>
-      <c r="I234" s="9" t="s">
+      <c r="I236" s="8" t="s">
         <v>515</v>
       </c>
-      <c r="J234" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="235" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="H235" s="9" t="s">
+      <c r="J236" s="11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="237" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="H237" s="9" t="s">
         <v>261</v>
       </c>
-      <c r="I235" s="9" t="s">
+      <c r="I237" s="9" t="s">
         <v>516</v>
       </c>
-      <c r="J235" s="12">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="236" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="H236" s="9" t="s">
+      <c r="J237" s="12">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="238" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="H238" s="8" t="s">
         <v>262</v>
       </c>
-      <c r="I236" s="9" t="s">
+      <c r="I238" s="8" t="s">
         <v>517</v>
       </c>
-      <c r="J236" s="12">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="237" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="H237" s="10" t="s">
+      <c r="J238" s="11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="239" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="H239" s="8" t="s">
         <v>263</v>
       </c>
-      <c r="I237" s="10" t="s">
+      <c r="I239" s="8" t="s">
         <v>518</v>
       </c>
-      <c r="J237" s="13">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="238" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="H238" s="9" t="s">
+      <c r="J239" s="11">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="240" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="H240" s="8" t="s">
         <v>264</v>
       </c>
-      <c r="I238" s="9" t="s">
+      <c r="I240" s="8" t="s">
         <v>519</v>
       </c>
-      <c r="J238" s="12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="239" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="H239" s="9" t="s">
+      <c r="J240" s="11">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="241" spans="8:10" x14ac:dyDescent="0.4">
+      <c r="H241" s="8" t="s">
         <v>265</v>
       </c>
-      <c r="I239" s="9" t="s">
+      <c r="I241" s="8" t="s">
         <v>520</v>
       </c>
-      <c r="J239" s="12">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="240" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="H240" s="9" t="s">
+      <c r="J241" s="11">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="242" spans="8:10" x14ac:dyDescent="0.4">
+      <c r="H242" s="8" t="s">
         <v>266</v>
       </c>
-      <c r="I240" s="9" t="s">
+      <c r="I242" s="8" t="s">
         <v>521</v>
       </c>
-      <c r="J240" s="12">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="241" spans="8:10" x14ac:dyDescent="0.4">
-      <c r="H241" s="9" t="s">
+      <c r="J242" s="11">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="243" spans="8:10" x14ac:dyDescent="0.4">
+      <c r="H243" s="8" t="s">
         <v>267</v>
       </c>
-      <c r="I241" s="9" t="s">
+      <c r="I243" s="8" t="s">
         <v>522</v>
       </c>
-      <c r="J241" s="12">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="242" spans="8:10" x14ac:dyDescent="0.4">
-      <c r="H242" s="9" t="s">
+      <c r="J243" s="11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="244" spans="8:10" x14ac:dyDescent="0.4">
+      <c r="H244" s="8" t="s">
         <v>268</v>
       </c>
-      <c r="I242" s="9" t="s">
+      <c r="I244" s="8" t="s">
         <v>523</v>
       </c>
-      <c r="J242" s="12">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="243" spans="8:10" x14ac:dyDescent="0.4">
-      <c r="H243" s="9" t="s">
+      <c r="J244" s="11">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="245" spans="8:10" x14ac:dyDescent="0.4">
+      <c r="H245" s="8" t="s">
         <v>269</v>
       </c>
-      <c r="I243" s="9" t="s">
+      <c r="I245" s="8" t="s">
         <v>524</v>
       </c>
-      <c r="J243" s="12">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="244" spans="8:10" x14ac:dyDescent="0.4">
-      <c r="H244" s="9" t="s">
+      <c r="J245" s="11">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="246" spans="8:10" x14ac:dyDescent="0.4">
+      <c r="H246" s="8" t="s">
         <v>270</v>
       </c>
-      <c r="I244" s="9" t="s">
+      <c r="I246" s="8" t="s">
         <v>525</v>
       </c>
-      <c r="J244" s="12">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="245" spans="8:10" x14ac:dyDescent="0.4">
-      <c r="H245" s="9" t="s">
+      <c r="J246" s="11">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="247" spans="8:10" x14ac:dyDescent="0.4">
+      <c r="H247" s="8" t="s">
         <v>271</v>
       </c>
-      <c r="I245" s="9" t="s">
+      <c r="I247" s="8" t="s">
         <v>526</v>
       </c>
-      <c r="J245" s="12">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="246" spans="8:10" x14ac:dyDescent="0.4">
-      <c r="H246" s="9" t="s">
+      <c r="J247" s="11">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="248" spans="8:10" x14ac:dyDescent="0.4">
+      <c r="H248" s="8" t="s">
         <v>272</v>
       </c>
-      <c r="I246" s="9" t="s">
+      <c r="I248" s="8" t="s">
         <v>527</v>
       </c>
-      <c r="J246" s="12">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="247" spans="8:10" x14ac:dyDescent="0.4">
-      <c r="H247" s="9" t="s">
+      <c r="J248" s="11">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="249" spans="8:10" x14ac:dyDescent="0.4">
+      <c r="H249" s="8" t="s">
         <v>273</v>
       </c>
-      <c r="I247" s="9" t="s">
+      <c r="I249" s="8" t="s">
         <v>528</v>
       </c>
-      <c r="J247" s="12">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="248" spans="8:10" x14ac:dyDescent="0.4">
-      <c r="H248" s="9" t="s">
+      <c r="J249" s="11">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="250" spans="8:10" x14ac:dyDescent="0.4">
+      <c r="H250" s="8" t="s">
         <v>274</v>
       </c>
-      <c r="I248" s="9" t="s">
+      <c r="I250" s="8" t="s">
         <v>529</v>
       </c>
-      <c r="J248" s="12">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="249" spans="8:10" x14ac:dyDescent="0.4">
-      <c r="H249" s="9" t="s">
+      <c r="J250" s="11">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="251" spans="8:10" x14ac:dyDescent="0.4">
+      <c r="H251" s="8" t="s">
         <v>275</v>
       </c>
-      <c r="I249" s="9" t="s">
+      <c r="I251" s="8" t="s">
         <v>530</v>
       </c>
-      <c r="J249" s="12">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="250" spans="8:10" x14ac:dyDescent="0.4">
-      <c r="H250" s="9" t="s">
+      <c r="J251" s="11">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="252" spans="8:10" x14ac:dyDescent="0.4">
+      <c r="H252" s="8" t="s">
         <v>276</v>
       </c>
-      <c r="I250" s="9" t="s">
+      <c r="I252" s="8" t="s">
         <v>531</v>
       </c>
-      <c r="J250" s="12">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="251" spans="8:10" x14ac:dyDescent="0.4">
-      <c r="H251" s="9" t="s">
+      <c r="J252" s="11">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="253" spans="8:10" x14ac:dyDescent="0.4">
+      <c r="H253" s="8" t="s">
         <v>277</v>
       </c>
-      <c r="I251" s="9" t="s">
+      <c r="I253" s="8" t="s">
         <v>532</v>
       </c>
-      <c r="J251" s="12">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="252" spans="8:10" x14ac:dyDescent="0.4">
-      <c r="H252" s="9" t="s">
+      <c r="J253" s="11">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="254" spans="8:10" x14ac:dyDescent="0.4">
+      <c r="H254" s="8" t="s">
         <v>278</v>
       </c>
-      <c r="I252" s="9" t="s">
+      <c r="I254" s="8" t="s">
         <v>533</v>
       </c>
-      <c r="J252" s="12">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="253" spans="8:10" x14ac:dyDescent="0.4">
-      <c r="H253" s="9" t="s">
+      <c r="J254" s="11">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="255" spans="8:10" x14ac:dyDescent="0.4">
+      <c r="H255" s="8" t="s">
         <v>279</v>
       </c>
-      <c r="I253" s="9" t="s">
+      <c r="I255" s="8" t="s">
         <v>534</v>
       </c>
-      <c r="J253" s="12">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="254" spans="8:10" x14ac:dyDescent="0.4">
-      <c r="H254" s="9" t="s">
+      <c r="J255" s="11">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="256" spans="8:10" x14ac:dyDescent="0.4">
+      <c r="H256" s="8" t="s">
         <v>280</v>
       </c>
-      <c r="I254" s="9" t="s">
+      <c r="I256" s="8" t="s">
         <v>535</v>
       </c>
-      <c r="J254" s="12">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="255" spans="8:10" x14ac:dyDescent="0.4">
-      <c r="H255" s="9" t="s">
+      <c r="J256" s="11">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="257" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="H257" s="8" t="s">
         <v>281</v>
       </c>
-      <c r="I255" s="9" t="s">
+      <c r="I257" s="8" t="s">
         <v>536</v>
       </c>
-      <c r="J255" s="12">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="256" spans="8:10" x14ac:dyDescent="0.4">
-      <c r="H256" s="9" t="s">
+      <c r="J257" s="11">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="258" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="H258" s="8" t="s">
         <v>282</v>
       </c>
-      <c r="I256" s="9" t="s">
+      <c r="I258" s="8" t="s">
         <v>537</v>
       </c>
-      <c r="J256" s="12">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="257" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="H257" s="9" t="s">
+      <c r="J258" s="11">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="259" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="H259" s="8" t="s">
         <v>283</v>
       </c>
-      <c r="I257" s="9" t="s">
+      <c r="I259" s="8" t="s">
         <v>538</v>
       </c>
-      <c r="J257" s="12">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="258" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="H258" s="9" t="s">
+      <c r="J259" s="11">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="260" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="H260" s="8" t="s">
         <v>284</v>
       </c>
-      <c r="I258" s="9" t="s">
+      <c r="I260" s="8" t="s">
         <v>539</v>
       </c>
-      <c r="J258" s="12">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="259" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="H259" s="9" t="s">
+      <c r="J260" s="11">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="261" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="H261" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="I261" s="8" t="s">
+        <v>540</v>
+      </c>
+      <c r="J261" s="11">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="262" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="H262" s="8" t="s">
         <v>285</v>
       </c>
-      <c r="I259" s="9" t="s">
-        <v>540</v>
-      </c>
-      <c r="J259" s="12">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="260" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="H260" s="9" t="s">
+      <c r="I262" s="8" t="s">
+        <v>541</v>
+      </c>
+      <c r="J262" s="11">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="263" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="H263" s="8" t="s">
         <v>286</v>
       </c>
-      <c r="I260" s="9" t="s">
-        <v>541</v>
-      </c>
-      <c r="J260" s="12">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="261" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="H261" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="I261" s="9" t="s">
+      <c r="I263" s="8" t="s">
         <v>542</v>
       </c>
-      <c r="J261" s="12">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="262" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="H262" s="9" t="s">
+      <c r="J263" s="11">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="264" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="H264" s="8" t="s">
         <v>287</v>
       </c>
-      <c r="I262" s="9" t="s">
+      <c r="I264" s="8" t="s">
         <v>543</v>
       </c>
-      <c r="J262" s="12">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="263" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="H263" s="9" t="s">
+      <c r="J264" s="11">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="265" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="H265" s="8" t="s">
         <v>288</v>
       </c>
-      <c r="I263" s="9" t="s">
+      <c r="I265" s="8" t="s">
         <v>544</v>
       </c>
-      <c r="J263" s="12">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="264" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="H264" s="9" t="s">
+      <c r="J265" s="11">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="266" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="H266" s="9" t="s">
         <v>289</v>
       </c>
-      <c r="I264" s="9" t="s">
+      <c r="I266" s="8" t="s">
         <v>545</v>
       </c>
-      <c r="J264" s="12">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="265" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="H265" s="9" t="s">
+      <c r="J266" s="11">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="267" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="H267" s="9" t="s">
         <v>290</v>
       </c>
-      <c r="I265" s="9" t="s">
+      <c r="I267" s="8" t="s">
         <v>546</v>
       </c>
-      <c r="J265" s="12">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="266" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="H266" s="10" t="s">
+      <c r="J267" s="11">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="268" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="H268" s="9" t="s">
         <v>291</v>
       </c>
-      <c r="I266" s="9" t="s">
+      <c r="I268" s="8" t="s">
         <v>547</v>
       </c>
-      <c r="J266" s="12">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="267" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="H267" s="10" t="s">
+      <c r="J268" s="11">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="269" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="H269" s="9" t="s">
         <v>292</v>
       </c>
-      <c r="I267" s="9" t="s">
+      <c r="I269" s="8" t="s">
         <v>548</v>
       </c>
-      <c r="J267" s="12">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="268" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="H268" s="10" t="s">
-        <v>293</v>
-      </c>
-      <c r="I268" s="9" t="s">
-        <v>549</v>
-      </c>
-      <c r="J268" s="12">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="269" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="H269" s="10" t="s">
-        <v>294</v>
-      </c>
-      <c r="I269" s="9" t="s">
-        <v>550</v>
-      </c>
-      <c r="J269" s="12">
+      <c r="J269" s="11">
         <v>36</v>
       </c>
     </row>
@@ -5653,22 +5667,22 @@
       <c r="D270" t="b">
         <v>1</v>
       </c>
-      <c r="H270" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="I270" s="9" t="s">
-        <v>551</v>
-      </c>
-      <c r="J270" s="12">
+      <c r="H270" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="I270" s="8" t="s">
+        <v>549</v>
+      </c>
+      <c r="J270" s="11">
         <v>0</v>
       </c>
     </row>
     <row r="271" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H271" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="I271" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="J271">
         <v>1</v>
@@ -5676,10 +5690,10 @@
     </row>
     <row r="272" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H272" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="I272" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="J272">
         <v>2</v>
@@ -5687,10 +5701,10 @@
     </row>
     <row r="273" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H273" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="I273" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="J273">
         <v>3</v>
@@ -5698,10 +5712,10 @@
     </row>
     <row r="274" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H274" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="I274" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="J274">
         <v>4</v>
@@ -5709,10 +5723,10 @@
     </row>
     <row r="275" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H275" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="I275" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="J275">
         <v>5</v>
@@ -5720,10 +5734,10 @@
     </row>
     <row r="276" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H276" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="I276" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="J276">
         <v>6</v>
@@ -5731,10 +5745,10 @@
     </row>
     <row r="277" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H277" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="I277" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="J277">
         <v>7</v>
@@ -5751,10 +5765,10 @@
         <v>1</v>
       </c>
       <c r="H278" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I278" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="J278">
         <v>0</v>
@@ -5762,10 +5776,10 @@
     </row>
     <row r="279" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H279" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="I279" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="J279">
         <v>1</v>
@@ -5782,10 +5796,10 @@
         <v>1</v>
       </c>
       <c r="H280" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I280" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="J280">
         <v>0</v>
@@ -5793,10 +5807,10 @@
     </row>
     <row r="281" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H281" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="I281" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="J281">
         <v>1</v>
@@ -5804,10 +5818,10 @@
     </row>
     <row r="282" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H282" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="I282" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="J282">
         <v>2</v>
@@ -5815,10 +5829,10 @@
     </row>
     <row r="283" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H283" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="I283" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="J283">
         <v>3</v>
@@ -5826,10 +5840,10 @@
     </row>
     <row r="284" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H284" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="I284" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="J284">
         <v>4</v>
@@ -5846,10 +5860,10 @@
         <v>1</v>
       </c>
       <c r="H285" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="I285" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="J285">
         <v>0</v>
@@ -5857,18 +5871,18 @@
     </row>
     <row r="286" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H286" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="I286" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="J286">
         <v>1</v>
       </c>
     </row>
     <row r="287" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B287" t="s">
-        <v>61</v>
+      <c r="B287" s="14" t="s">
+        <v>586</v>
       </c>
       <c r="C287" t="b">
         <v>0</v>
@@ -5877,10 +5891,10 @@
         <v>1</v>
       </c>
       <c r="H287" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="I287" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="J287">
         <v>0</v>
@@ -5888,18 +5902,18 @@
     </row>
     <row r="288" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H288" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="I288" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="J288">
         <v>1</v>
       </c>
     </row>
     <row r="289" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B289" t="s">
-        <v>62</v>
+      <c r="B289" s="14" t="s">
+        <v>587</v>
       </c>
       <c r="C289" t="b">
         <v>0</v>
@@ -5908,10 +5922,10 @@
         <v>1</v>
       </c>
       <c r="H289" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="I289" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="J289">
         <v>1</v>
@@ -5919,10 +5933,10 @@
     </row>
     <row r="290" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H290" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="I290" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="J290">
         <v>2</v>
@@ -5930,7 +5944,7 @@
     </row>
     <row r="291" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B291" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C291" t="b">
         <v>0</v>
@@ -5939,10 +5953,10 @@
         <v>1</v>
       </c>
       <c r="H291" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="I291" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="J291">
         <v>1</v>
@@ -5950,10 +5964,10 @@
     </row>
     <row r="292" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H292" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="I292" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="J292">
         <v>2</v>
@@ -5961,7 +5975,7 @@
     </row>
     <row r="293" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B293" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C293" t="b">
         <v>0</v>
@@ -5970,10 +5984,10 @@
         <v>1</v>
       </c>
       <c r="H293" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="I293" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="J293">
         <v>1</v>
@@ -5981,10 +5995,10 @@
     </row>
     <row r="294" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H294" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="I294" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="J294">
         <v>2</v>
@@ -5992,7 +6006,7 @@
     </row>
     <row r="295" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B295" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C295" t="b">
         <v>0</v>
@@ -6001,10 +6015,10 @@
         <v>1</v>
       </c>
       <c r="H295" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="I295" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="J295">
         <v>1</v>
@@ -6012,10 +6026,10 @@
     </row>
     <row r="296" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H296" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="I296" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="J296">
         <v>2</v>
@@ -6023,10 +6037,10 @@
     </row>
     <row r="297" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H297" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="I297" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="J297">
         <v>3</v>
@@ -6034,7 +6048,7 @@
     </row>
     <row r="298" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B298" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C298" t="b">
         <v>0</v>
@@ -6042,33 +6056,33 @@
       <c r="D298" t="b">
         <v>1</v>
       </c>
-      <c r="H298" s="10" t="s">
+      <c r="H298" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="I298" t="s">
+        <v>573</v>
+      </c>
+      <c r="J298">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="299" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="H299" s="7" t="s">
         <v>201</v>
       </c>
-      <c r="I298" t="s">
-        <v>575</v>
-      </c>
-      <c r="J298">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="299" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="H299" s="8" t="s">
-        <v>203</v>
-      </c>
       <c r="I299" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="J299">
         <v>2</v>
       </c>
     </row>
     <row r="300" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="H300" s="8" t="s">
-        <v>143</v>
+      <c r="H300" s="7" t="s">
+        <v>141</v>
       </c>
       <c r="I300" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="J300">
         <v>3</v>
@@ -6076,7 +6090,7 @@
     </row>
     <row r="301" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B301" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C301" t="b">
         <v>0</v>
@@ -6084,44 +6098,44 @@
       <c r="D301" t="b">
         <v>1</v>
       </c>
-      <c r="H301" s="10" t="s">
-        <v>312</v>
+      <c r="H301" s="9" t="s">
+        <v>310</v>
       </c>
       <c r="I301" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="J301">
         <v>1</v>
       </c>
     </row>
     <row r="302" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="H302" s="8" t="s">
-        <v>202</v>
+      <c r="H302" s="7" t="s">
+        <v>200</v>
       </c>
       <c r="I302" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="J302">
         <v>2</v>
       </c>
     </row>
     <row r="303" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="H303" s="8" t="s">
-        <v>143</v>
+      <c r="H303" s="7" t="s">
+        <v>141</v>
       </c>
       <c r="I303" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="J303">
         <v>3</v>
       </c>
     </row>
     <row r="304" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="H304" s="8" t="s">
-        <v>313</v>
+      <c r="H304" s="7" t="s">
+        <v>311</v>
       </c>
       <c r="I304" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="J304">
         <v>4</v>
@@ -6129,7 +6143,7 @@
     </row>
     <row r="305" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B305" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C305" t="b">
         <v>0</v>
@@ -6137,77 +6151,77 @@
       <c r="D305" t="b">
         <v>1</v>
       </c>
-      <c r="H305" s="10" t="s">
-        <v>200</v>
+      <c r="H305" s="9" t="s">
+        <v>198</v>
       </c>
       <c r="I305" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="J305">
         <v>1</v>
       </c>
     </row>
     <row r="306" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="H306" s="8" t="s">
-        <v>203</v>
+      <c r="H306" s="7" t="s">
+        <v>201</v>
       </c>
       <c r="I306" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="J306">
         <v>2</v>
       </c>
     </row>
     <row r="307" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="H307" s="8" t="s">
-        <v>202</v>
+      <c r="H307" s="7" t="s">
+        <v>200</v>
       </c>
       <c r="I307" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="J307">
         <v>3</v>
       </c>
     </row>
     <row r="308" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="H308" s="8" t="s">
-        <v>143</v>
+      <c r="H308" s="7" t="s">
+        <v>141</v>
       </c>
       <c r="I308" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="J308">
         <v>4</v>
       </c>
     </row>
     <row r="309" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="H309" s="8" t="s">
-        <v>204</v>
+      <c r="H309" s="7" t="s">
+        <v>202</v>
       </c>
       <c r="I309" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="J309">
         <v>5</v>
       </c>
     </row>
     <row r="310" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="H310" s="8" t="s">
-        <v>205</v>
+      <c r="H310" s="7" t="s">
+        <v>203</v>
       </c>
       <c r="I310" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="J310">
         <v>6</v>
       </c>
     </row>
     <row r="311" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="H311" s="8" t="s">
-        <v>313</v>
+      <c r="H311" s="7" t="s">
+        <v>311</v>
       </c>
       <c r="I311" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="J311">
         <v>7</v>
@@ -6215,7 +6229,7 @@
     </row>
     <row r="312" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B312" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C312" t="b">
         <v>0</v>
@@ -6224,10 +6238,10 @@
         <v>1</v>
       </c>
       <c r="H312" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="I312" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="J312">
         <v>1</v>
@@ -6235,10 +6249,10 @@
     </row>
     <row r="313" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H313" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="I313" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="J313">
         <v>2</v>
